--- a/Arquivo de estudantes/Cadastro de estudantes/Lista de estudantes.xlsx
+++ b/Arquivo de estudantes/Cadastro de estudantes/Lista de estudantes.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>Nome</t>
   </si>
@@ -81,6 +81,15 @@
   </si>
   <si>
     <t>Amelia</t>
+  </si>
+  <si>
+    <t>Alice Da Rosa Julio</t>
+  </si>
+  <si>
+    <t>Luisa Julio</t>
+  </si>
+  <si>
+    <t>15 de agosto</t>
   </si>
 </sst>
 </file>
@@ -710,20 +719,44 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="3"/>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="13">
+        <v>19</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="2">
+        <v>12</v>
+      </c>
+      <c r="I16" s="3">
+        <v>842797796</v>
+      </c>
     </row>
     <row r="17" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D17" s="1"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="3"/>
+      <c r="D17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13">
+        <v>20</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="2">
+        <v>12</v>
+      </c>
+      <c r="I17" s="3">
+        <v>841991635</v>
+      </c>
     </row>
     <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="1"/>
